--- a/experiment_results/combined_sweep/rtt_bursts_S4_atk10pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S4_atk10pct_wu500000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.2</t>
+          <t>00:010.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:015.8</t>
+          <t>00:018.5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110.4</t>
+          <t>109.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>265.2</t>
+          <t>177.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>96.91</t>
+          <t>98.66</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>230760</t>
+          <t>292748</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,37 +590,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:021.9</t>
+          <t>00:030.5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>674.3</t>
+          <t>177.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>527.1</t>
+          <t>227.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>479052</t>
+          <t>738161</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:038.4</t>
+          <t>00:039.5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1163.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>522.0</t>
+          <t>181.9</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>501344</t>
+          <t>973826</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:051.3</t>
+          <t>00:048.3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1009.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>428.2</t>
+          <t>219.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,17 +734,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>531109</t>
+          <t>1169164</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:052.0</t>
+          <t>00:059.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1136.8</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>421.0</t>
+          <t>236.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>556130</t>
+          <t>1340966</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -810,6 +810,747 @@
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>01:006.8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>190.6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>319.9</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7.95</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1519689</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>01:021.9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>299.1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>399.1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1724297</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>01:030.0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>153.6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>237.2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1845681</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>01:038.5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>152.1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>223.8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1948204</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>01:050.5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>198.7</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>276.7</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2066999</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>02:000.4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>145.3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>221.1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2148886</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>02:008.7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>145.7</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>204.5</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2214739</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>02:019.9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>154.1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>219.7</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2268023</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>02:030.2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>126.7</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>200.4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2307675</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>02:040.4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>118.6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>183.2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>5.92</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2344648</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>02:049.7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>107.2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>171.2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>7.27</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2374508</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>02:056.0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>114.4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>198.1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>7.85</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2391582</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03:000.8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2393088</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>DDoS Burst</t>
         </is>
